--- a/research/traditional_assets/database/data/netherlands/netherlands_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_bank_money_center.xlsx
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0228</v>
+        <v>-0.013</v>
       </c>
       <c r="E2">
-        <v>-0.00683</v>
-      </c>
-      <c r="F2">
-        <v>0.244</v>
+        <v>-0.066</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>5285.1</v>
+        <v>3461.5</v>
       </c>
       <c r="L2">
-        <v>0.2574229937459817</v>
+        <v>0.213269996180055</v>
       </c>
       <c r="M2">
-        <v>2099.2892</v>
+        <v>3720.912</v>
       </c>
       <c r="N2">
-        <v>0.03993511580349075</v>
+        <v>0.0854519691621559</v>
       </c>
       <c r="O2">
-        <v>0.3972089837467598</v>
+        <v>1.07494207713419</v>
       </c>
       <c r="P2">
-        <v>2099.2892</v>
+        <v>3720.912</v>
       </c>
       <c r="Q2">
-        <v>0.03993511580349075</v>
+        <v>0.0854519691621559</v>
       </c>
       <c r="R2">
-        <v>0.3972089837467598</v>
+        <v>1.07494207713419</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>148100.4</v>
+        <v>132466.2</v>
       </c>
       <c r="V2">
-        <v>2.817337708660294</v>
+        <v>3.042129896495261</v>
       </c>
       <c r="W2">
-        <v>0.08303430029411026</v>
+        <v>0.05387146174293593</v>
       </c>
       <c r="X2">
-        <v>0.1173963369847676</v>
+        <v>0.1427058163190829</v>
       </c>
       <c r="Y2">
-        <v>-0.03436203669065731</v>
+        <v>-0.08883435457614698</v>
       </c>
       <c r="Z2">
-        <v>0.1194933632258808</v>
+        <v>0.1086607372991139</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03870928813866681</v>
+        <v>0.06121510551155092</v>
       </c>
       <c r="AC2">
-        <v>-0.03870928813866681</v>
+        <v>-0.06121510551155092</v>
       </c>
       <c r="AD2">
-        <v>233215.1</v>
+        <v>173898.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>233215.1</v>
+        <v>173898.8</v>
       </c>
       <c r="AG2">
-        <v>85114.70000000001</v>
+        <v>41432.59999999998</v>
       </c>
       <c r="AH2">
-        <v>0.8160577305966145</v>
+        <v>0.7997454041915411</v>
       </c>
       <c r="AI2">
-        <v>0.7811197624906596</v>
+        <v>0.7743786225494911</v>
       </c>
       <c r="AJ2">
-        <v>0.6181968329965675</v>
+        <v>0.4875771536836654</v>
       </c>
       <c r="AK2">
-        <v>0.5656788602243583</v>
+        <v>0.4498682944731452</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0228</v>
+        <v>-0.013</v>
       </c>
       <c r="E3">
-        <v>-0.00683</v>
-      </c>
-      <c r="F3">
-        <v>0.244</v>
+        <v>-0.066</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>5285.1</v>
+        <v>3461.5</v>
       </c>
       <c r="L3">
-        <v>0.2574229937459817</v>
+        <v>0.213269996180055</v>
       </c>
       <c r="M3">
-        <v>2099.2892</v>
+        <v>3720.912</v>
       </c>
       <c r="N3">
-        <v>0.03993511580349075</v>
+        <v>0.0854519691621559</v>
       </c>
       <c r="O3">
-        <v>0.3972089837467598</v>
+        <v>1.07494207713419</v>
       </c>
       <c r="P3">
-        <v>2099.2892</v>
+        <v>3720.912</v>
       </c>
       <c r="Q3">
-        <v>0.03993511580349075</v>
+        <v>0.0854519691621559</v>
       </c>
       <c r="R3">
-        <v>0.3972089837467598</v>
+        <v>1.07494207713419</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>148100.4</v>
+        <v>132466.2</v>
       </c>
       <c r="V3">
-        <v>2.817337708660294</v>
+        <v>3.042129896495261</v>
       </c>
       <c r="W3">
-        <v>0.08303430029411026</v>
+        <v>0.05387146174293593</v>
       </c>
       <c r="X3">
-        <v>0.1173963369847676</v>
+        <v>0.1427058163190829</v>
       </c>
       <c r="Y3">
-        <v>-0.03436203669065731</v>
+        <v>-0.08883435457614698</v>
       </c>
       <c r="Z3">
-        <v>0.1194933632258808</v>
+        <v>0.1086607372991139</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03870928813866681</v>
+        <v>0.06121510551155092</v>
       </c>
       <c r="AC3">
-        <v>-0.03870928813866681</v>
+        <v>-0.06121510551155092</v>
       </c>
       <c r="AD3">
-        <v>233215.1</v>
+        <v>173898.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>233215.1</v>
+        <v>173898.8</v>
       </c>
       <c r="AG3">
-        <v>85114.70000000001</v>
+        <v>41432.59999999998</v>
       </c>
       <c r="AH3">
-        <v>0.8160577305966145</v>
+        <v>0.7997454041915411</v>
       </c>
       <c r="AI3">
-        <v>0.7811197624906596</v>
+        <v>0.7743786225494911</v>
       </c>
       <c r="AJ3">
-        <v>0.6181968329965675</v>
+        <v>0.4875771536836654</v>
       </c>
       <c r="AK3">
-        <v>0.5656788602243583</v>
+        <v>0.4498682944731452</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_bank_money_center.xlsx
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.013</v>
+        <v>0.142</v>
       </c>
       <c r="E2">
-        <v>-0.066</v>
+        <v>0.28</v>
+      </c>
+      <c r="F2">
+        <v>0.3</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3461.5</v>
+        <v>16160</v>
       </c>
       <c r="L2">
-        <v>0.213269996180055</v>
+        <v>0.4483322097284761</v>
       </c>
       <c r="M2">
-        <v>3720.912</v>
+        <v>2026.934</v>
       </c>
       <c r="N2">
-        <v>0.0854519691621559</v>
+        <v>0.04026527875723835</v>
       </c>
       <c r="O2">
-        <v>1.07494207713419</v>
+        <v>0.1254290841584158</v>
       </c>
       <c r="P2">
-        <v>3720.912</v>
+        <v>2026.934</v>
       </c>
       <c r="Q2">
-        <v>0.0854519691621559</v>
+        <v>0.04026527875723835</v>
       </c>
       <c r="R2">
-        <v>1.07494207713419</v>
+        <v>0.1254290841584158</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>132466.2</v>
+        <v>123544.7</v>
       </c>
       <c r="V2">
-        <v>3.042129896495261</v>
+        <v>2.45422977979519</v>
       </c>
       <c r="W2">
-        <v>0.05387146174293593</v>
+        <v>0.3212972775225117</v>
       </c>
       <c r="X2">
-        <v>0.1427058163190829</v>
+        <v>0.1313769931324947</v>
       </c>
       <c r="Y2">
-        <v>-0.08883435457614698</v>
+        <v>0.189920284390017</v>
       </c>
       <c r="Z2">
-        <v>0.1086607372991139</v>
+        <v>0.3929489897927257</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06121510551155092</v>
+        <v>0.05204698442906083</v>
       </c>
       <c r="AC2">
-        <v>-0.06121510551155092</v>
+        <v>-0.05204698442906083</v>
       </c>
       <c r="AD2">
-        <v>173898.8</v>
+        <v>279015.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>173898.8</v>
+        <v>279015.7</v>
       </c>
       <c r="AG2">
-        <v>41432.59999999998</v>
+        <v>155471</v>
       </c>
       <c r="AH2">
-        <v>0.7997454041915411</v>
+        <v>0.8471574154590545</v>
       </c>
       <c r="AI2">
-        <v>0.7743786225494911</v>
+        <v>0.8338362467645836</v>
       </c>
       <c r="AJ2">
-        <v>0.4875771536836654</v>
+        <v>0.75540849470751</v>
       </c>
       <c r="AK2">
-        <v>0.4498682944731452</v>
+        <v>0.7365773417816273</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.013</v>
+        <v>0.142</v>
       </c>
       <c r="E3">
-        <v>-0.066</v>
+        <v>0.28</v>
+      </c>
+      <c r="F3">
+        <v>0.3</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3461.5</v>
+        <v>16160</v>
       </c>
       <c r="L3">
-        <v>0.213269996180055</v>
+        <v>0.4483322097284761</v>
       </c>
       <c r="M3">
-        <v>3720.912</v>
+        <v>2026.934</v>
       </c>
       <c r="N3">
-        <v>0.0854519691621559</v>
+        <v>0.04026527875723835</v>
       </c>
       <c r="O3">
-        <v>1.07494207713419</v>
+        <v>0.1254290841584158</v>
       </c>
       <c r="P3">
-        <v>3720.912</v>
+        <v>2026.934</v>
       </c>
       <c r="Q3">
-        <v>0.0854519691621559</v>
+        <v>0.04026527875723835</v>
       </c>
       <c r="R3">
-        <v>1.07494207713419</v>
+        <v>0.1254290841584158</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>132466.2</v>
+        <v>123544.7</v>
       </c>
       <c r="V3">
-        <v>3.042129896495261</v>
+        <v>2.45422977979519</v>
       </c>
       <c r="W3">
-        <v>0.05387146174293593</v>
+        <v>0.3212972775225117</v>
       </c>
       <c r="X3">
-        <v>0.1427058163190829</v>
+        <v>0.1313769931324947</v>
       </c>
       <c r="Y3">
-        <v>-0.08883435457614698</v>
+        <v>0.189920284390017</v>
       </c>
       <c r="Z3">
-        <v>0.1086607372991139</v>
+        <v>0.3929489897927257</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06121510551155092</v>
+        <v>0.05204698442906083</v>
       </c>
       <c r="AC3">
-        <v>-0.06121510551155092</v>
+        <v>-0.05204698442906083</v>
       </c>
       <c r="AD3">
-        <v>173898.8</v>
+        <v>279015.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>173898.8</v>
+        <v>279015.7</v>
       </c>
       <c r="AG3">
-        <v>41432.59999999998</v>
+        <v>155471</v>
       </c>
       <c r="AH3">
-        <v>0.7997454041915411</v>
+        <v>0.8471574154590545</v>
       </c>
       <c r="AI3">
-        <v>0.7743786225494911</v>
+        <v>0.8338362467645836</v>
       </c>
       <c r="AJ3">
-        <v>0.4875771536836654</v>
+        <v>0.75540849470751</v>
       </c>
       <c r="AK3">
-        <v>0.4498682944731452</v>
+        <v>0.7365773417816273</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.142</v>
+        <v>-0.00468</v>
       </c>
       <c r="E2">
-        <v>0.28</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="F2">
-        <v>0.3</v>
+        <v>-0.00156</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>16160</v>
+        <v>4070.9</v>
       </c>
       <c r="L2">
-        <v>0.4483322097284761</v>
+        <v>0.2121088967044419</v>
       </c>
       <c r="M2">
-        <v>2026.934</v>
+        <v>3832.926</v>
       </c>
       <c r="N2">
-        <v>0.04026527875723835</v>
+        <v>0.07852329111745737</v>
       </c>
       <c r="O2">
-        <v>0.1254290841584158</v>
+        <v>0.9415426564150433</v>
       </c>
       <c r="P2">
-        <v>2026.934</v>
+        <v>3832.926</v>
       </c>
       <c r="Q2">
-        <v>0.04026527875723835</v>
+        <v>0.07852329111745737</v>
       </c>
       <c r="R2">
-        <v>0.1254290841584158</v>
+        <v>0.9415426564150433</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>123544.7</v>
+        <v>111664.1</v>
       </c>
       <c r="V2">
-        <v>2.45422977979519</v>
+        <v>2.2876081175762</v>
       </c>
       <c r="W2">
-        <v>0.3212972775225117</v>
+        <v>0.07437131765243206</v>
       </c>
       <c r="X2">
-        <v>0.1313769931324947</v>
+        <v>0.1294224302111002</v>
       </c>
       <c r="Y2">
-        <v>0.189920284390017</v>
+        <v>-0.05505111255866811</v>
       </c>
       <c r="Z2">
-        <v>0.3929489897927257</v>
+        <v>0.09130220709438486</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05204698442906083</v>
+        <v>0.05515227379618871</v>
       </c>
       <c r="AC2">
-        <v>-0.05204698442906083</v>
+        <v>-0.05515227379618871</v>
       </c>
       <c r="AD2">
-        <v>279015.7</v>
+        <v>256756.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>279015.7</v>
+        <v>256756.6</v>
       </c>
       <c r="AG2">
-        <v>155471</v>
+        <v>145092.5</v>
       </c>
       <c r="AH2">
-        <v>0.8471574154590545</v>
+        <v>0.8402568059869908</v>
       </c>
       <c r="AI2">
-        <v>0.8338362467645836</v>
+        <v>0.8150599525864751</v>
       </c>
       <c r="AJ2">
-        <v>0.75540849470751</v>
+        <v>0.748265517513464</v>
       </c>
       <c r="AK2">
-        <v>0.7365773417816273</v>
+        <v>0.7135059244706825</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.142</v>
+        <v>-0.00468</v>
       </c>
       <c r="E3">
-        <v>0.28</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="F3">
-        <v>0.3</v>
+        <v>-0.00156</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>16160</v>
+        <v>4070.9</v>
       </c>
       <c r="L3">
-        <v>0.4483322097284761</v>
+        <v>0.2121088967044419</v>
       </c>
       <c r="M3">
-        <v>2026.934</v>
+        <v>3832.926</v>
       </c>
       <c r="N3">
-        <v>0.04026527875723835</v>
+        <v>0.07852329111745737</v>
       </c>
       <c r="O3">
-        <v>0.1254290841584158</v>
+        <v>0.9415426564150433</v>
       </c>
       <c r="P3">
-        <v>2026.934</v>
+        <v>3832.926</v>
       </c>
       <c r="Q3">
-        <v>0.04026527875723835</v>
+        <v>0.07852329111745737</v>
       </c>
       <c r="R3">
-        <v>0.1254290841584158</v>
+        <v>0.9415426564150433</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>123544.7</v>
+        <v>111664.1</v>
       </c>
       <c r="V3">
-        <v>2.45422977979519</v>
+        <v>2.2876081175762</v>
       </c>
       <c r="W3">
-        <v>0.3212972775225117</v>
+        <v>0.07437131765243206</v>
       </c>
       <c r="X3">
-        <v>0.1313769931324947</v>
+        <v>0.1294224302111002</v>
       </c>
       <c r="Y3">
-        <v>0.189920284390017</v>
+        <v>-0.05505111255866811</v>
       </c>
       <c r="Z3">
-        <v>0.3929489897927257</v>
+        <v>0.09130220709438486</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05204698442906083</v>
+        <v>0.05515227379618871</v>
       </c>
       <c r="AC3">
-        <v>-0.05204698442906083</v>
+        <v>-0.05515227379618871</v>
       </c>
       <c r="AD3">
-        <v>279015.7</v>
+        <v>256756.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>279015.7</v>
+        <v>256756.6</v>
       </c>
       <c r="AG3">
-        <v>155471</v>
+        <v>145092.5</v>
       </c>
       <c r="AH3">
-        <v>0.8471574154590545</v>
+        <v>0.8402568059869908</v>
       </c>
       <c r="AI3">
-        <v>0.8338362467645836</v>
+        <v>0.8150599525864751</v>
       </c>
       <c r="AJ3">
-        <v>0.75540849470751</v>
+        <v>0.748265517513464</v>
       </c>
       <c r="AK3">
-        <v>0.7365773417816273</v>
+        <v>0.7135059244706825</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_bank_money_center.xlsx
@@ -648,10 +648,10 @@
         <v>0.07437131765243206</v>
       </c>
       <c r="X2">
-        <v>0.1294224302111002</v>
+        <v>0.1293686684233891</v>
       </c>
       <c r="Y2">
-        <v>-0.05505111255866811</v>
+        <v>-0.05499735077095703</v>
       </c>
       <c r="Z2">
         <v>0.09130220709438486</v>
@@ -660,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05515227379618871</v>
+        <v>0.0551436857165039</v>
       </c>
       <c r="AC2">
-        <v>-0.05515227379618871</v>
+        <v>-0.0551436857165039</v>
       </c>
       <c r="AD2">
         <v>256756.6</v>
@@ -773,10 +773,10 @@
         <v>0.07437131765243206</v>
       </c>
       <c r="X3">
-        <v>0.1294224302111002</v>
+        <v>0.1293686684233891</v>
       </c>
       <c r="Y3">
-        <v>-0.05505111255866811</v>
+        <v>-0.05499735077095703</v>
       </c>
       <c r="Z3">
         <v>0.09130220709438486</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05515227379618871</v>
+        <v>0.0551436857165039</v>
       </c>
       <c r="AC3">
-        <v>-0.05515227379618871</v>
+        <v>-0.0551436857165039</v>
       </c>
       <c r="AD3">
         <v>256756.6</v>
